--- a/uranai/data/生まれ年グループ.xlsx
+++ b/uranai/data/生まれ年グループ.xlsx
@@ -1811,1596 +1811,1510 @@
   </sheetPr>
   <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>配信スケジュール(週×順)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>金曜の占いで使う生まれ年を1行ずつ並べた表。</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>順番</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>生まれ年</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>和暦</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1983年</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>昭和58年</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1997年</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>平成9年</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1958年</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>昭和33年</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1980年</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>昭和55年</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1996年</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>平成8年</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1986年</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>昭和61年</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1999年</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>平成11年</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1965年</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>昭和40年</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1990年</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>平成2年</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>1989年</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>昭和64年/平成元年</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>1979年</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>昭和54年</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2006年</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>平成18年</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2011年</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>平成23年</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2016年</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>平成28年</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2002年</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>平成14年</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="A20" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>1957年</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>昭和32年</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2009年</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>平成21年</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n">
+      <c r="A22" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>1975年</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>昭和50年</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="A23" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" t="n">
         <v>9</v>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2008年</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>平成20年</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n">
+      <c r="A24" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>1968年</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>昭和43年</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n">
+      <c r="A25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2014年</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>平成26年</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n">
+      <c r="A26" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>1969年</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>昭和44年</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n">
+      <c r="A27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>1970年</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>昭和45年</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n">
+      <c r="A28" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2005年</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>平成17年</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
+      <c r="A29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2000年</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>平成12年</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n">
+      <c r="A30" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2022年</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>令和4年</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="A31" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2007年</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>平成19年</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n">
+      <c r="A32" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" t="n">
         <v>8</v>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2015年</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>平成27年</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n">
+      <c r="A33" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" t="n">
         <v>9</v>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>1992年</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>平成4年</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n">
+      <c r="A34" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" t="n">
         <v>10</v>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2001年</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>平成13年</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n">
+      <c r="A35" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>1973年</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>昭和48年</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n">
+      <c r="A36" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>1952年</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>昭和27年</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n">
+      <c r="A37" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>1966年</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>昭和41年</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n">
+      <c r="A38" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2003年</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>平成15年</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n">
+      <c r="A39" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>1972年</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>昭和47年</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n">
+      <c r="A40" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2010年</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>平成22年</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n">
+      <c r="A41" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>1974年</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>昭和49年</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n">
+      <c r="A42" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" t="n">
         <v>8</v>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>1955年</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>昭和30年</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n">
+      <c r="A43" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" t="n">
         <v>9</v>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>1956年</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>昭和31年</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
+      <c r="A44" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" t="n">
         <v>10</v>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>1993年</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>平成5年</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
+      <c r="A45" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2019年</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>平成31年/令和元年</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
+      <c r="A46" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>1959年</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>昭和34年</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
+      <c r="A47" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>1998年</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>平成10年</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
+      <c r="A48" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>1971年</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>昭和46年</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
+      <c r="A49" t="n">
         <v>5</v>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2013年</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>平成25年</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
+      <c r="A50" t="n">
         <v>5</v>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>2017年</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>平成29年</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n">
+      <c r="A51" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" t="n">
         <v>7</v>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>1960年</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>昭和35年</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n">
+      <c r="A52" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B52" t="n">
         <v>8</v>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>1950年</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>昭和25年</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n">
+      <c r="A53" t="n">
         <v>5</v>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" t="n">
         <v>9</v>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>2020年</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>令和2年</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n">
+      <c r="A54" t="n">
         <v>5</v>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" t="n">
         <v>10</v>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>1987年</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>昭和62年</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n">
+      <c r="A55" t="n">
         <v>6</v>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>2021年</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>令和3年</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n">
+      <c r="A56" t="n">
         <v>6</v>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2012年</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>平成24年</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
+      <c r="A57" t="n">
         <v>6</v>
       </c>
-      <c r="B57" s="16" t="n">
+      <c r="B57" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>1976年</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>昭和51年</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n">
+      <c r="A58" t="n">
         <v>6</v>
       </c>
-      <c r="B58" s="16" t="n">
+      <c r="B58" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>1984年</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>昭和59年</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n">
+      <c r="A59" t="n">
         <v>6</v>
       </c>
-      <c r="B59" s="16" t="n">
+      <c r="B59" t="n">
         <v>5</v>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>1994年</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>平成6年</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n">
+      <c r="A60" t="n">
         <v>6</v>
       </c>
-      <c r="B60" s="16" t="n">
+      <c r="B60" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>1991年</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>平成3年</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n">
+      <c r="A61" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="16" t="n">
+      <c r="B61" t="n">
         <v>7</v>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>1995年</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>平成7年</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n">
+      <c r="A62" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="16" t="n">
+      <c r="B62" t="n">
         <v>8</v>
       </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>1962年</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>昭和37年</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n">
+      <c r="A63" t="n">
         <v>6</v>
       </c>
-      <c r="B63" s="16" t="n">
+      <c r="B63" t="n">
         <v>9</v>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>令和5年</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n">
+      <c r="A64" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="16" t="n">
+      <c r="B64" t="n">
         <v>10</v>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>1951年</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>昭和26年</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n">
+      <c r="A65" t="n">
         <v>7</v>
       </c>
-      <c r="B65" s="16" t="n">
+      <c r="B65" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>1988年</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>昭和63年</t>
         </is>
       </c>
-      <c r="E65" s="17" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n">
+      <c r="A66" t="n">
         <v>7</v>
       </c>
-      <c r="B66" s="16" t="n">
+      <c r="B66" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>1982年</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>昭和57年</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n">
+      <c r="A67" t="n">
         <v>7</v>
       </c>
-      <c r="B67" s="16" t="n">
+      <c r="B67" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="16" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>令和7年</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n">
+      <c r="A68" t="n">
         <v>7</v>
       </c>
-      <c r="B68" s="16" t="n">
+      <c r="B68" t="n">
         <v>4</v>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>1977年</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>昭和52年</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n">
+      <c r="A69" t="n">
         <v>7</v>
       </c>
-      <c r="B69" s="16" t="n">
+      <c r="B69" t="n">
         <v>5</v>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>2018年</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>平成30年</t>
         </is>
       </c>
-      <c r="E69" s="17" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n">
+      <c r="A70" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="16" t="n">
+      <c r="B70" t="n">
         <v>6</v>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>2024年</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>令和6年</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n">
+      <c r="A71" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="16" t="n">
+      <c r="B71" t="n">
         <v>7</v>
       </c>
-      <c r="C71" s="16" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>1954年</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>昭和29年</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n">
+      <c r="A72" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="16" t="n">
+      <c r="B72" t="n">
         <v>8</v>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>2004年</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>平成16年</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n">
+      <c r="A73" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="16" t="n">
+      <c r="B73" t="n">
         <v>9</v>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>1961年</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>昭和36年</t>
         </is>
       </c>
-      <c r="E73" s="17" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n">
+      <c r="A74" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="16" t="n">
+      <c r="B74" t="n">
         <v>10</v>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>1963年</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>昭和38年</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n">
+      <c r="A75" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="16" t="n">
+      <c r="B75" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="16" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>1967年</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>昭和42年</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n">
+      <c r="A76" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="16" t="n">
+      <c r="B76" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="16" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>1978年</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>昭和53年</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n">
+      <c r="A77" t="n">
         <v>8</v>
       </c>
-      <c r="B77" s="16" t="n">
+      <c r="B77" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>1981年</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>昭和56年</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n">
+      <c r="A78" t="n">
         <v>8</v>
       </c>
-      <c r="B78" s="16" t="n">
+      <c r="B78" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>1985年</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>昭和60年</t>
         </is>
       </c>
-      <c r="E78" s="17" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n">
+      <c r="A79" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="16" t="n">
+      <c r="B79" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>1953年</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>昭和28年</t>
         </is>
       </c>
-      <c r="E79" s="17" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n">
+      <c r="A80" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="16" t="n">
+      <c r="B80" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>1964年</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>昭和39年</t>
         </is>
       </c>
-      <c r="E80" s="17" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="n">
+      <c r="A81" t="n">
         <v>8</v>
       </c>
-      <c r="B81" s="18" t="n">
+      <c r="B81" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="18" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>1983年</t>
         </is>
       </c>
-      <c r="D81" s="19" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>昭和58年</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="n">
+      <c r="A82" t="n">
         <v>8</v>
       </c>
-      <c r="B82" s="18" t="n">
+      <c r="B82" t="n">
         <v>8</v>
       </c>
-      <c r="C82" s="18" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>1997年</t>
         </is>
       </c>
-      <c r="D82" s="19" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>平成9年</t>
         </is>
       </c>
-      <c r="E82" s="19" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="n">
+      <c r="A83" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="18" t="n">
+      <c r="B83" t="n">
         <v>9</v>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>1958年</t>
         </is>
       </c>
-      <c r="D83" s="19" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>昭和33年</t>
         </is>
       </c>
-      <c r="E83" s="19" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="n">
+      <c r="A84" t="n">
         <v>8</v>
       </c>
-      <c r="B84" s="18" t="n">
+      <c r="B84" t="n">
         <v>10</v>
       </c>
-      <c r="C84" s="18" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>1980年</t>
         </is>
       </c>
-      <c r="D84" s="19" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>昭和55年</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/uranai/data/生まれ年グループ.xlsx
+++ b/uranai/data/生まれ年グループ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用ルール_必読" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グループ一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配信スケジュール" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全年リスト_時系列" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="運用ルール_必読" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="グループ一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="配信スケジュール" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="全年リスト_時系列" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
